--- a/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
@@ -81,7 +81,7 @@
     <x:t>Cherry Mae Anub</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">OZONE ROBLEDO LABRADA </x:t>
+    <x:t>OZONE ROBLEDO LABRADA</x:t>
   </x:si>
   <x:si>
     <x:t>Poblacion, Guipos, Zamboanga Del Sur</x:t>

--- a/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
@@ -9,58 +9,22 @@
     <x:sheet name="January 2026" sheetId="7" r:id="rId7"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
+    <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
     <x:definedName name="summary">#REF!</x:definedName>
   </x:definedNames>
   <x:calcPr/>
   <x:extLst>
     <x:ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="M1zy22YtJ+TLWEM7ow84Ac98JQFmbAbmONakZm1eVcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Gqj+nP2ZfjBIlYJvjiPFyqmWD9usEriw94U1uDhyO0="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
-  <x:si>
-    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Application Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPANY NAME / NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS(NEW/REN/DUP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PERMIT NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REFERENCE NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE OF FILING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXPIRATION DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+  <x:si>
+    <x:t>{{Name}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur</x:t>
@@ -139,7 +103,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -166,12 +130,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13.0"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
@@ -179,6 +137,27 @@
       <x:sz val="11.0"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="13.0"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -193,13 +172,6 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -244,12 +216,12 @@
   <x:borders count="14">
     <x:border/>
     <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF000000"/>
-      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
@@ -261,14 +233,14 @@
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
@@ -450,7 +422,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="23">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -461,176 +433,194 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0" shrinkToFit="0" readingOrder="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0" shrinkToFit="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -894,336 +884,312 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s"/>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s"/>
       <x:c r="E6" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>46035.1020949074</x:v>
       </x:c>
-      <x:c r="I6" s="12">
+      <x:c r="I6" s="13">
         <x:v>46035.1021180556</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="n">
+      <x:c r="J6" s="12" t="n">
         <x:v>1231234312123</x:v>
       </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="K6" s="14" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="15">
         <x:v>46035.1127430556</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s"/>
-      <x:c r="E7" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D7" s="16" t="s"/>
+      <x:c r="E7" s="16" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F7" s="16" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G7" s="16" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H7" s="17">
         <x:v>46035.3508680556</x:v>
       </x:c>
-      <x:c r="I7" s="12">
+      <x:c r="I7" s="17">
         <x:v>46035.3508796296</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="n">
+      <x:c r="J7" s="16" t="n">
         <x:v>5555</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="n">
+      <x:c r="K7" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L7" s="12">
+      <x:c r="L7" s="17">
         <x:v>46035.3565856482</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="M7" s="16" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="19" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C8" s="19" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D8" s="19" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E8" s="19" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F8" s="19" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G8" s="19" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H8" s="16">
+      <x:c r="H8" s="20">
         <x:v>46040.9500115741</x:v>
       </x:c>
-      <x:c r="I8" s="16">
+      <x:c r="I8" s="20">
         <x:v>46040.9500462963</x:v>
       </x:c>
-      <x:c r="J8" s="15" t="n">
+      <x:c r="J8" s="19" t="n">
         <x:v>1111</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="K8" s="21" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="18">
+      <x:c r="L8" s="20">
         <x:v>46040.9546990741</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>18</x:v>
+      <x:c r="M8" s="19" t="s">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="B9" s="19" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C9" s="19" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D9" s="19" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E9" s="19" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F9" s="19" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
+      <x:c r="G9" s="19" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H9" s="20">
         <x:v>46036.033587963</x:v>
       </x:c>
-      <x:c r="I9" s="16">
+      <x:c r="I9" s="20">
         <x:v>46036.0336226852</x:v>
       </x:c>
-      <x:c r="J9" s="15" t="n">
+      <x:c r="J9" s="19" t="n">
         <x:v>125646</x:v>
       </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="K9" s="21" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L9" s="18">
+      <x:c r="L9" s="20">
         <x:v>46036.037337963</x:v>
       </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>18</x:v>
+      <x:c r="M9" s="19" t="s">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
+      <x:c r="B10" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H10" s="13">
         <x:v>46030.3123263889</x:v>
       </x:c>
-      <x:c r="I10" s="16">
+      <x:c r="I10" s="13">
         <x:v>46030.3123611111</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="J10" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="K10" s="14" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L10" s="18">
+      <x:c r="L10" s="15">
         <x:v>46030.5666550926</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>18</x:v>
+      <x:c r="M10" s="11" t="s">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="19" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C13" s="20" t="s"/>
-      <x:c r="D13" s="20" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="21" t="s"/>
+      <x:c r="B13" s="22" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C13" s="23" t="s"/>
+      <x:c r="D13" s="23" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="24" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="22" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="24" t="s">
-        <x:v>34</x:v>
+      <x:c r="B14" s="25" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="27" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="25" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="n">
+      <x:c r="B15" s="28" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C15" s="29" t="s"/>
+      <x:c r="D15" s="29" t="s"/>
+      <x:c r="E15" s="29" t="s"/>
+      <x:c r="F15" s="30" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="n">
+      <x:c r="B16" s="28" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="29" t="s"/>
+      <x:c r="F16" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C17" s="29" t="s"/>
-      <x:c r="D17" s="29" t="s"/>
-      <x:c r="E17" s="29" t="s"/>
-      <x:c r="F17" s="30" t="n">
+      <x:c r="B17" s="31" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C17" s="32" t="s"/>
+      <x:c r="D17" s="32" t="s"/>
+      <x:c r="E17" s="32" t="s"/>
+      <x:c r="F17" s="33" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
@@ -22,9 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
-  <x:si>
-    <x:t>{{Name}}</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+  <x:si>
+    <x:t>EVALUATOR SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDWARD THEEVALUATOR</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur</x:t>
@@ -869,7 +872,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -886,7 +891,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>46023</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -949,20 +954,20 @@
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s"/>
       <x:c r="E6" s="11" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H6" s="13">
         <x:v>46035.1020949074</x:v>
@@ -980,7 +985,7 @@
         <x:v>46035.1127430556</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
@@ -988,20 +993,20 @@
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C7" s="16" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D7" s="16" t="s"/>
       <x:c r="E7" s="16" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F7" s="16" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G7" s="16" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H7" s="17">
         <x:v>46035.3508680556</x:v>
@@ -1019,29 +1024,29 @@
         <x:v>46035.3565856482</x:v>
       </x:c>
       <x:c r="M7" s="16" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="19" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C8" s="19" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D8" s="19" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E8" s="19" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F8" s="19" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G8" s="19" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H8" s="20">
         <x:v>46040.9500115741</x:v>
@@ -1059,27 +1064,27 @@
         <x:v>46040.9546990741</x:v>
       </x:c>
       <x:c r="M8" s="19" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="19" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C9" s="19" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D9" s="19" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E9" s="19" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F9" s="19" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G9" s="19" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H9" s="20">
         <x:v>46036.033587963</x:v>
@@ -1097,27 +1102,27 @@
         <x:v>46036.037337963</x:v>
       </x:c>
       <x:c r="M9" s="19" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B10" s="11" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C10" s="11" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D10" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E10" s="11" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F10" s="11" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G10" s="11" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H10" s="13">
         <x:v>46030.3123263889</x:v>
@@ -1126,7 +1131,7 @@
         <x:v>46030.3123611111</x:v>
       </x:c>
       <x:c r="J10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K10" s="14" t="n">
         <x:v>210</x:v>
@@ -1135,66 +1140,66 @@
         <x:v>46030.5666550926</x:v>
       </x:c>
       <x:c r="M10" s="11" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="22" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C13" s="23" t="s"/>
-      <x:c r="D13" s="23" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="24" t="s"/>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="22" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="24" t="s"/>
     </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="25" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C14" s="26" t="s"/>
-      <x:c r="D14" s="26" t="s"/>
-      <x:c r="E14" s="26" t="s"/>
-      <x:c r="F14" s="27" t="s">
+    <x:row r="16" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B16" s="25" t="s">
         <x:v>22</x:v>
       </x:c>
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="s">
+        <x:v>23</x:v>
+      </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="28" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="29" t="s"/>
-      <x:c r="D15" s="29" t="s"/>
-      <x:c r="E15" s="29" t="s"/>
-      <x:c r="F15" s="30" t="n">
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="28" t="s">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="C17" s="29" t="s"/>
+      <x:c r="D17" s="29" t="s"/>
+      <x:c r="E17" s="29" t="s"/>
+      <x:c r="F17" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="28" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="30" t="n">
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="28" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="31" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C17" s="32" t="s"/>
-      <x:c r="D17" s="32" t="s"/>
-      <x:c r="E17" s="32" t="s"/>
-      <x:c r="F17" s="33" t="n">
+    <x:row r="19" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B19" s="31" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C19" s="32" t="s"/>
+      <x:c r="D19" s="32" t="s"/>
+      <x:c r="E19" s="32" t="s"/>
+      <x:c r="F19" s="33" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2170,14 +2175,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B13:F13"/>
-    <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B15:F15"/>
     <x:mergeCell ref="B16:E16"/>
     <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B19:E19"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
@@ -500,7 +500,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="40">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -536,6 +536,50 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -555,28 +599,8 @@
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -952,7 +976,7 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
@@ -990,7 +1014,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>2</x:v>
@@ -1106,97 +1130,123 @@
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="11" t="s">
+      <x:c r="B10" s="22" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C10" s="11" t="s">
+      <x:c r="C10" s="22" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D10" s="12" t="s">
+      <x:c r="D10" s="23" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E10" s="11" t="s">
+      <x:c r="E10" s="22" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F10" s="11" t="s">
+      <x:c r="F10" s="22" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G10" s="11" t="s">
+      <x:c r="G10" s="22" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H10" s="13">
+      <x:c r="H10" s="24">
         <x:v>46030.3123263889</x:v>
       </x:c>
-      <x:c r="I10" s="13">
+      <x:c r="I10" s="24">
         <x:v>46030.3123611111</x:v>
       </x:c>
-      <x:c r="J10" s="12" t="s">
+      <x:c r="J10" s="23" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K10" s="14" t="n">
+      <x:c r="K10" s="25" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L10" s="15">
+      <x:c r="L10" s="26">
         <x:v>46030.5666550926</x:v>
       </x:c>
-      <x:c r="M10" s="11" t="s">
+      <x:c r="M10" s="22" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B11" s="27" t="s"/>
+      <x:c r="C11" s="27" t="s"/>
+      <x:c r="D11" s="27" t="s"/>
+      <x:c r="E11" s="27" t="s"/>
+      <x:c r="F11" s="27" t="s"/>
+      <x:c r="G11" s="27" t="s"/>
+      <x:c r="H11" s="27" t="s"/>
+      <x:c r="I11" s="27" t="s"/>
+      <x:c r="J11" s="27" t="s"/>
+      <x:c r="K11" s="27" t="s"/>
+      <x:c r="L11" s="27" t="s"/>
+      <x:c r="M11" s="27" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B12" s="27" t="s"/>
+      <x:c r="C12" s="27" t="s"/>
+      <x:c r="D12" s="27" t="s"/>
+      <x:c r="E12" s="27" t="s"/>
+      <x:c r="F12" s="27" t="s"/>
+      <x:c r="G12" s="27" t="s"/>
+      <x:c r="H12" s="27" t="s"/>
+      <x:c r="I12" s="27" t="s"/>
+      <x:c r="J12" s="27" t="s"/>
+      <x:c r="K12" s="27" t="s"/>
+      <x:c r="L12" s="27" t="s"/>
+      <x:c r="M12" s="27" t="s"/>
+    </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="22" t="s">
+      <x:c r="B15" s="28" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="24" t="s"/>
+      <x:c r="C15" s="29" t="s"/>
+      <x:c r="D15" s="29" t="s"/>
+      <x:c r="E15" s="30" t="s"/>
+      <x:c r="F15" s="30" t="s"/>
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="25" t="s">
+      <x:c r="B16" s="31" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="s">
+      <x:c r="C16" s="32" t="s"/>
+      <x:c r="D16" s="32" t="s"/>
+      <x:c r="E16" s="32" t="s"/>
+      <x:c r="F16" s="33" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="28" t="s">
+      <x:c r="B17" s="34" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C17" s="29" t="s"/>
-      <x:c r="D17" s="29" t="s"/>
-      <x:c r="E17" s="29" t="s"/>
-      <x:c r="F17" s="30" t="n">
+      <x:c r="C17" s="35" t="s"/>
+      <x:c r="D17" s="35" t="s"/>
+      <x:c r="E17" s="35" t="s"/>
+      <x:c r="F17" s="36" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="28" t="s">
+      <x:c r="B18" s="34" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C18" s="29" t="s"/>
-      <x:c r="D18" s="29" t="s"/>
-      <x:c r="E18" s="29" t="s"/>
-      <x:c r="F18" s="30" t="n">
+      <x:c r="C18" s="35" t="s"/>
+      <x:c r="D18" s="35" t="s"/>
+      <x:c r="E18" s="35" t="s"/>
+      <x:c r="F18" s="36" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="31" t="s">
+      <x:c r="B19" s="37" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C19" s="32" t="s"/>
-      <x:c r="D19" s="32" t="s"/>
-      <x:c r="E19" s="32" t="s"/>
-      <x:c r="F19" s="33" t="n">
+      <x:c r="C19" s="38" t="s"/>
+      <x:c r="D19" s="38" t="s"/>
+      <x:c r="E19" s="38" t="s"/>
+      <x:c r="F19" s="39" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
@@ -946,7 +946,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -1014,7 +1014,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>2</x:v>

--- a/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
@@ -22,12 +22,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>EDWARD THEEVALUATOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur</x:t>
@@ -106,7 +142,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -151,21 +187,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
@@ -175,6 +196,13 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -425,7 +453,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="23">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -436,71 +464,65 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="40">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -531,56 +553,8 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -595,59 +569,71 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -948,18 +934,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -977,276 +951,288 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46035.1020949074</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46035.1021180556</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1231234312123</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>46035.1127430556</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="16" t="s">
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D7" s="16" t="s"/>
-      <x:c r="E7" s="16" t="s">
+      <x:c r="I7" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="F7" s="16" t="s">
+      <x:c r="J7" s="10" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G7" s="16" t="s">
+      <x:c r="K7" s="10" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="H7" s="17">
-        <x:v>46035.3508680556</x:v>
-      </x:c>
-      <x:c r="I7" s="17">
-        <x:v>46035.3508796296</x:v>
-      </x:c>
-      <x:c r="J7" s="16" t="n">
-        <x:v>5555</x:v>
-      </x:c>
-      <x:c r="K7" s="18" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L7" s="17">
-        <x:v>46035.3565856482</x:v>
-      </x:c>
-      <x:c r="M7" s="16" t="s">
-        <x:v>7</x:v>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="19" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="19" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E8" s="19" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F8" s="19" t="s">
+      <x:c r="B8" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="G8" s="19" t="s">
+      <x:c r="C8" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="H8" s="20">
-        <x:v>46040.9500115741</x:v>
-      </x:c>
-      <x:c r="I8" s="20">
-        <x:v>46040.9500462963</x:v>
-      </x:c>
-      <x:c r="J8" s="19" t="n">
-        <x:v>1111</x:v>
-      </x:c>
-      <x:c r="K8" s="21" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L8" s="20">
-        <x:v>46040.9546990741</x:v>
-      </x:c>
-      <x:c r="M8" s="19" t="s">
-        <x:v>7</x:v>
+      <x:c r="D8" s="11" t="s"/>
+      <x:c r="E8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46035.1020949074</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46035.1021180556</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1231234312123</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46035.1127430556</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="19" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C9" s="19" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="19" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E9" s="19" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F9" s="19" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G9" s="19" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H9" s="20">
-        <x:v>46036.033587963</x:v>
-      </x:c>
-      <x:c r="I9" s="20">
-        <x:v>46036.0336226852</x:v>
-      </x:c>
-      <x:c r="J9" s="19" t="n">
-        <x:v>125646</x:v>
-      </x:c>
-      <x:c r="K9" s="21" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L9" s="20">
-        <x:v>46036.037337963</x:v>
-      </x:c>
-      <x:c r="M9" s="19" t="s">
-        <x:v>7</x:v>
+      <x:c r="B9" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s"/>
+      <x:c r="E9" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46035.3508680556</x:v>
+      </x:c>
+      <x:c r="I9" s="12">
+        <x:v>46035.3508796296</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>5555</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46035.3565856482</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="22" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C10" s="22" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="23" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E10" s="22" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F10" s="22" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G10" s="22" t="s">
+      <x:c r="B10" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46040.9500115741</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>46040.9500462963</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="n">
+        <x:v>1111</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L10" s="18">
+        <x:v>46040.9546990741</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H10" s="24">
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46036.033587963</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46036.0336226852</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="n">
+        <x:v>125646</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L11" s="18">
+        <x:v>46036.037337963</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
         <x:v>46030.3123263889</x:v>
       </x:c>
-      <x:c r="I10" s="24">
+      <x:c r="I12" s="16">
         <x:v>46030.3123611111</x:v>
       </x:c>
-      <x:c r="J10" s="23" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="K10" s="25" t="n">
+      <x:c r="J12" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L10" s="26">
+      <x:c r="L12" s="18">
         <x:v>46030.5666550926</x:v>
       </x:c>
-      <x:c r="M10" s="22" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B11" s="27" t="s"/>
-      <x:c r="C11" s="27" t="s"/>
-      <x:c r="D11" s="27" t="s"/>
-      <x:c r="E11" s="27" t="s"/>
-      <x:c r="F11" s="27" t="s"/>
-      <x:c r="G11" s="27" t="s"/>
-      <x:c r="H11" s="27" t="s"/>
-      <x:c r="I11" s="27" t="s"/>
-      <x:c r="J11" s="27" t="s"/>
-      <x:c r="K11" s="27" t="s"/>
-      <x:c r="L11" s="27" t="s"/>
-      <x:c r="M11" s="27" t="s"/>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B12" s="27" t="s"/>
-      <x:c r="C12" s="27" t="s"/>
-      <x:c r="D12" s="27" t="s"/>
-      <x:c r="E12" s="27" t="s"/>
-      <x:c r="F12" s="27" t="s"/>
-      <x:c r="G12" s="27" t="s"/>
-      <x:c r="H12" s="27" t="s"/>
-      <x:c r="I12" s="27" t="s"/>
-      <x:c r="J12" s="27" t="s"/>
-      <x:c r="K12" s="27" t="s"/>
-      <x:c r="L12" s="27" t="s"/>
-      <x:c r="M12" s="27" t="s"/>
+      <x:c r="M12" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="28" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C15" s="29" t="s"/>
-      <x:c r="D15" s="29" t="s"/>
-      <x:c r="E15" s="30" t="s"/>
-      <x:c r="F15" s="30" t="s"/>
+      <x:c r="B15" s="19" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C15" s="20" t="s"/>
+      <x:c r="D15" s="20" t="s"/>
+      <x:c r="E15" s="21" t="s"/>
+      <x:c r="F15" s="21" t="s"/>
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="31" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C16" s="32" t="s"/>
-      <x:c r="D16" s="32" t="s"/>
-      <x:c r="E16" s="32" t="s"/>
-      <x:c r="F16" s="33" t="s">
-        <x:v>23</x:v>
+      <x:c r="B16" s="22" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C16" s="23" t="s"/>
+      <x:c r="D16" s="23" t="s"/>
+      <x:c r="E16" s="23" t="s"/>
+      <x:c r="F16" s="24" t="s">
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="34" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="s"/>
-      <x:c r="D17" s="35" t="s"/>
-      <x:c r="E17" s="35" t="s"/>
-      <x:c r="F17" s="36" t="n">
+      <x:c r="B17" s="25" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="34" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C18" s="35" t="s"/>
-      <x:c r="D18" s="35" t="s"/>
-      <x:c r="E18" s="35" t="s"/>
-      <x:c r="F18" s="36" t="n">
+      <x:c r="B18" s="25" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="37" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C19" s="38" t="s"/>
-      <x:c r="D19" s="38" t="s"/>
-      <x:c r="E19" s="38" t="s"/>
-      <x:c r="F19" s="39" t="n">
+      <x:c r="B19" s="28" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C19" s="29" t="s"/>
+      <x:c r="D19" s="29" t="s"/>
+      <x:c r="E19" s="29" t="s"/>
+      <x:c r="F19" s="30" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
@@ -22,12 +22,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>EDWARD THEEVALUATOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XIII | January 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -142,7 +145,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -182,6 +185,30 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -453,14 +480,23 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="23">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -473,56 +509,56 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -553,87 +589,99 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -862,58 +910,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -956,283 +1004,283 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s"/>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="G8" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46035.1020949074</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="15">
         <x:v>46035.1021180556</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1231234312123</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>46035.1127430556</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>19</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="B9" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>46035.3508680556</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>46035.3508796296</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>5555</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46035.3565856482</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="s"/>
-      <x:c r="E9" s="11" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H9" s="12">
-        <x:v>46035.3508680556</x:v>
-      </x:c>
-      <x:c r="I9" s="12">
-        <x:v>46035.3508796296</x:v>
-      </x:c>
-      <x:c r="J9" s="11" t="n">
-        <x:v>5555</x:v>
-      </x:c>
-      <x:c r="K9" s="13" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L9" s="12">
-        <x:v>46035.3565856482</x:v>
-      </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
+      <x:c r="B10" s="17" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="C10" s="17" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="D10" s="18" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="E10" s="17" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="H10" s="16">
+      <x:c r="G10" s="17" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H10" s="19">
         <x:v>46040.9500115741</x:v>
       </x:c>
-      <x:c r="I10" s="16">
+      <x:c r="I10" s="19">
         <x:v>46040.9500462963</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="n">
+      <x:c r="J10" s="18" t="n">
         <x:v>1111</x:v>
       </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="K10" s="20" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L10" s="18">
+      <x:c r="L10" s="21">
         <x:v>46040.9546990741</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>19</x:v>
+      <x:c r="M10" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
+      <x:c r="B11" s="17" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="E11" s="14" t="s">
+      <x:c r="C11" s="17" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
+      <x:c r="D11" s="18" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E11" s="17" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="H11" s="16">
+      <x:c r="G11" s="17" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
         <x:v>46036.033587963</x:v>
       </x:c>
-      <x:c r="I11" s="16">
+      <x:c r="I11" s="19">
         <x:v>46036.0336226852</x:v>
       </x:c>
-      <x:c r="J11" s="15" t="n">
+      <x:c r="J11" s="18" t="n">
         <x:v>125646</x:v>
       </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="K11" s="20" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L11" s="18">
+      <x:c r="L11" s="21">
         <x:v>46036.037337963</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>19</x:v>
+      <x:c r="M11" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
+      <x:c r="B12" s="17" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="E12" s="14" t="s">
+      <x:c r="C12" s="17" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
+      <x:c r="D12" s="18" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E12" s="17" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H12" s="16">
+      <x:c r="G12" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H12" s="19">
         <x:v>46030.3123263889</x:v>
       </x:c>
-      <x:c r="I12" s="16">
+      <x:c r="I12" s="19">
         <x:v>46030.3123611111</x:v>
       </x:c>
-      <x:c r="J12" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
+      <x:c r="J12" s="18" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="K12" s="20" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L12" s="18">
+      <x:c r="L12" s="21">
         <x:v>46030.5666550926</x:v>
       </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>19</x:v>
+      <x:c r="M12" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="19" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C15" s="20" t="s"/>
-      <x:c r="D15" s="20" t="s"/>
-      <x:c r="E15" s="21" t="s"/>
-      <x:c r="F15" s="21" t="s"/>
+      <x:c r="B15" s="22" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="24" t="s"/>
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="22" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C16" s="23" t="s"/>
-      <x:c r="D16" s="23" t="s"/>
-      <x:c r="E16" s="23" t="s"/>
-      <x:c r="F16" s="24" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>35</x:v>
+      </x:c>
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="s">
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="25" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="n">
+      <x:c r="B17" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C17" s="29" t="s"/>
+      <x:c r="D17" s="29" t="s"/>
+      <x:c r="E17" s="29" t="s"/>
+      <x:c r="F17" s="30" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="25" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C18" s="26" t="s"/>
-      <x:c r="D18" s="26" t="s"/>
-      <x:c r="E18" s="26" t="s"/>
-      <x:c r="F18" s="27" t="n">
+      <x:c r="B18" s="28" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="28" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C19" s="29" t="s"/>
-      <x:c r="D19" s="29" t="s"/>
-      <x:c r="E19" s="29" t="s"/>
-      <x:c r="F19" s="30" t="n">
+      <x:c r="B19" s="31" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C19" s="32" t="s"/>
+      <x:c r="D19" s="32" t="s"/>
+      <x:c r="E19" s="32" t="s"/>
+      <x:c r="F19" s="33" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -2214,7 +2262,7 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B15:F15"/>
     <x:mergeCell ref="B16:E16"/>
     <x:mergeCell ref="B17:E17"/>

--- a/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -67,6 +67,42 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ApplicationType}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Name}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Status}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Address}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.PermitNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ReferenceNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DateOfFiling}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ExpirationDate}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Amount}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DatePaid}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur</x:t>
@@ -142,10 +178,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
+    <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
+    <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="15">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -190,15 +228,7 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="16"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF0000FF"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -214,15 +244,8 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -480,26 +503,26 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -509,56 +532,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -589,99 +615,91 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -910,78 +928,90 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
-    <x:row r="4" spans="1:28">
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28">
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1002,7 +1032,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1042,250 +1072,300 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="C8" s="9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="D8" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="E8" s="9" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="F8" s="9" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46035.1020949074</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>46035.1021180556</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1231234312123</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46035.1127430556</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
+      <x:c r="G8" s="9" t="s">
         <x:v>20</x:v>
       </x:c>
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
       <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46035.3508680556</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>46035.3508796296</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>5555</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46035.3565856482</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E10" s="17" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
+      <x:c r="B10" s="15" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="G10" s="17" t="s">
+      <x:c r="C10" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="H10" s="19">
-        <x:v>46040.9500115741</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>46040.9500462963</x:v>
-      </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1111</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L10" s="21">
-        <x:v>46040.9546990741</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>46035.1020949074</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>46035.1021180556</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="n">
+        <x:v>1231234312123</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>46035.1127430556</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E11" s="17" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H11" s="19">
-        <x:v>46036.033587963</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>46036.0336226852</x:v>
-      </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>125646</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L11" s="21">
-        <x:v>46036.037337963</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="B11" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s"/>
+      <x:c r="E11" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>46035.3508680556</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>46035.3508796296</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="n">
+        <x:v>5555</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>46035.3565856482</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E12" s="17" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
+      <x:c r="B12" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>46040.9500115741</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>46040.9500462963</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="n">
+        <x:v>1111</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>46040.9546990741</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H12" s="19">
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>46036.033587963</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>46036.0336226852</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="n">
+        <x:v>125646</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>46036.037337963</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
         <x:v>46030.3123263889</x:v>
       </x:c>
-      <x:c r="I12" s="19">
+      <x:c r="I14" s="17">
         <x:v>46030.3123611111</x:v>
       </x:c>
-      <x:c r="J12" s="18" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
+      <x:c r="J14" s="16" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L12" s="21">
+      <x:c r="L14" s="19">
         <x:v>46030.5666550926</x:v>
       </x:c>
-      <x:c r="M12" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="M14" s="15" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="22" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="24" t="s"/>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="20" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C17" s="21" t="s"/>
+      <x:c r="D17" s="21" t="s"/>
+      <x:c r="E17" s="22" t="s"/>
+      <x:c r="F17" s="22" t="s"/>
     </x:row>
-    <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="s">
-        <x:v>36</x:v>
+    <x:row r="18" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B18" s="23" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C18" s="24" t="s"/>
+      <x:c r="D18" s="24" t="s"/>
+      <x:c r="E18" s="24" t="s"/>
+      <x:c r="F18" s="25" t="s">
+        <x:v>48</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C17" s="29" t="s"/>
-      <x:c r="D17" s="29" t="s"/>
-      <x:c r="E17" s="29" t="s"/>
-      <x:c r="F17" s="30" t="n">
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="26" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="s"/>
+      <x:c r="D19" s="27" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="28" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C18" s="29" t="s"/>
-      <x:c r="D18" s="29" t="s"/>
-      <x:c r="E18" s="29" t="s"/>
-      <x:c r="F18" s="30" t="n">
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="26" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="31" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C19" s="32" t="s"/>
-      <x:c r="D19" s="32" t="s"/>
-      <x:c r="E19" s="32" t="s"/>
-      <x:c r="F19" s="33" t="n">
+    <x:row r="21" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B21" s="29" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C21" s="30" t="s"/>
+      <x:c r="D21" s="30" t="s"/>
+      <x:c r="E21" s="30" t="s"/>
+      <x:c r="F21" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2259,15 +2339,16 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="8">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
+  <x:mergeCells count="9">
+    <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B15:F15"/>
-    <x:mergeCell ref="B16:E16"/>
-    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B17:F17"/>
     <x:mergeCell ref="B18:E18"/>
     <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B21:E21"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -67,42 +67,6 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ApplicationType}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Name}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Status}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Address}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.PermitNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ReferenceNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DateOfFiling}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ExpirationDate}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Amount}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DatePaid}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur</x:t>
@@ -183,7 +147,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -227,14 +191,6 @@
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
-      <x:sz val="16"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
@@ -246,6 +202,21 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -503,7 +474,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="27">
+  <x:cellStyleXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -511,16 +482,16 @@
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -532,13 +503,7 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -550,41 +515,50 @@
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -615,28 +589,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -651,55 +617,71 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1032,7 +1014,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1072,297 +1054,247 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="9" t="s">
+      <x:c r="H8" s="15">
+        <x:v>46035.1020949074</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46035.1021180556</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1231234312123</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46035.1127430556</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="9" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
+      <x:c r="H9" s="15">
+        <x:v>46035.3508680556</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>46035.3508796296</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>5555</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46035.3565856482</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E10" s="17" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="G10" s="17" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46035.1020949074</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>46035.1021180556</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1231234312123</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46035.1127430556</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>32</x:v>
+      <x:c r="H10" s="19">
+        <x:v>46040.9500115741</x:v>
+      </x:c>
+      <x:c r="I10" s="19">
+        <x:v>46040.9500462963</x:v>
+      </x:c>
+      <x:c r="J10" s="18" t="n">
+        <x:v>1111</x:v>
+      </x:c>
+      <x:c r="K10" s="20" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L10" s="21">
+        <x:v>46040.9546990741</x:v>
+      </x:c>
+      <x:c r="M10" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>46035.3508680556</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>46035.3508796296</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>5555</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>46035.3565856482</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>32</x:v>
+      <x:c r="B11" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E11" s="17" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
+        <x:v>46036.033587963</x:v>
+      </x:c>
+      <x:c r="I11" s="19">
+        <x:v>46036.0336226852</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="n">
+        <x:v>125646</x:v>
+      </x:c>
+      <x:c r="K11" s="20" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L11" s="21">
+        <x:v>46036.037337963</x:v>
+      </x:c>
+      <x:c r="M11" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>46040.9500115741</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>46040.9500462963</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1111</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="B12" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E12" s="17" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G12" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H12" s="19">
+        <x:v>46030.3123263889</x:v>
+      </x:c>
+      <x:c r="I12" s="19">
+        <x:v>46030.3123611111</x:v>
+      </x:c>
+      <x:c r="J12" s="18" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="K12" s="20" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L12" s="19">
-        <x:v>46040.9546990741</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>32</x:v>
+      <x:c r="L12" s="21">
+        <x:v>46030.5666550926</x:v>
+      </x:c>
+      <x:c r="M12" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E13" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
-        <x:v>46036.033587963</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>46036.0336226852</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>125646</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L13" s="19">
-        <x:v>46036.037337963</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D14" s="16" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E14" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F14" s="15" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H14" s="17">
-        <x:v>46030.3123263889</x:v>
-      </x:c>
-      <x:c r="I14" s="17">
-        <x:v>46030.3123611111</x:v>
-      </x:c>
-      <x:c r="J14" s="16" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="K14" s="18" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L14" s="19">
-        <x:v>46030.5666550926</x:v>
-      </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="20" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C17" s="21" t="s"/>
-      <x:c r="D17" s="21" t="s"/>
-      <x:c r="E17" s="22" t="s"/>
-      <x:c r="F17" s="22" t="s"/>
+      <x:c r="B17" s="22" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C17" s="23" t="s"/>
+      <x:c r="D17" s="23" t="s"/>
+      <x:c r="E17" s="24" t="s"/>
+      <x:c r="F17" s="24" t="s"/>
     </x:row>
     <x:row r="18" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B18" s="23" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="s"/>
-      <x:c r="D18" s="24" t="s"/>
-      <x:c r="E18" s="24" t="s"/>
-      <x:c r="F18" s="25" t="s">
-        <x:v>48</x:v>
+      <x:c r="B18" s="25" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="s">
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
+      <x:c r="B19" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C19" s="29" t="s"/>
+      <x:c r="D19" s="29" t="s"/>
+      <x:c r="E19" s="29" t="s"/>
+      <x:c r="F19" s="30" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
+      <x:c r="B20" s="28" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C20" s="29" t="s"/>
+      <x:c r="D20" s="29" t="s"/>
+      <x:c r="E20" s="29" t="s"/>
+      <x:c r="F20" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B21" s="29" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C21" s="30" t="s"/>
-      <x:c r="D21" s="30" t="s"/>
-      <x:c r="E21" s="30" t="s"/>
-      <x:c r="F21" s="31" t="n">
+      <x:c r="B21" s="31" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C21" s="32" t="s"/>
+      <x:c r="D21" s="32" t="s"/>
+      <x:c r="E21" s="32" t="s"/>
+      <x:c r="F21" s="33" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
@@ -1243,61 +1243,61 @@
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="22" t="s">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="22" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C17" s="23" t="s"/>
-      <x:c r="D17" s="23" t="s"/>
-      <x:c r="E17" s="24" t="s"/>
-      <x:c r="F17" s="24" t="s"/>
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="24" t="s"/>
     </x:row>
-    <x:row r="18" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B18" s="25" t="s">
+    <x:row r="16" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B16" s="25" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C18" s="26" t="s"/>
-      <x:c r="D18" s="26" t="s"/>
-      <x:c r="E18" s="26" t="s"/>
-      <x:c r="F18" s="27" t="s">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="s">
         <x:v>36</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="28" t="s">
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="28" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C19" s="29" t="s"/>
-      <x:c r="D19" s="29" t="s"/>
-      <x:c r="E19" s="29" t="s"/>
-      <x:c r="F19" s="30" t="n">
+      <x:c r="C17" s="29" t="s"/>
+      <x:c r="D17" s="29" t="s"/>
+      <x:c r="E17" s="29" t="s"/>
+      <x:c r="F17" s="30" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="28" t="s">
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="28" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C20" s="29" t="s"/>
-      <x:c r="D20" s="29" t="s"/>
-      <x:c r="E20" s="29" t="s"/>
-      <x:c r="F20" s="30" t="n">
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B21" s="31" t="s">
+    <x:row r="19" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B19" s="31" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C21" s="32" t="s"/>
-      <x:c r="D21" s="32" t="s"/>
-      <x:c r="E21" s="32" t="s"/>
-      <x:c r="F21" s="33" t="n">
+      <x:c r="C19" s="32" t="s"/>
+      <x:c r="D19" s="32" t="s"/>
+      <x:c r="E19" s="32" t="s"/>
+      <x:c r="F19" s="33" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2276,11 +2276,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B17:F17"/>
+    <x:mergeCell ref="B15:F15"/>
+    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
     <x:mergeCell ref="B19:E19"/>
-    <x:mergeCell ref="B20:E20"/>
-    <x:mergeCell ref="B21:E21"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -84,6 +84,9 @@
     <x:t>61-1-2026-1018-872</x:t>
   </x:si>
   <x:si>
+    <x:t>1231234312123</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cherry Mae Anub</x:t>
   </x:si>
   <x:si>
@@ -99,6 +102,9 @@
     <x:t>61-1-2026-1019-426</x:t>
   </x:si>
   <x:si>
+    <x:t>5555</x:t>
+  </x:si>
+  <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
   </x:si>
   <x:si>
@@ -111,10 +117,16 @@
     <x:t>70-1-2026-1028-697</x:t>
   </x:si>
   <x:si>
+    <x:t>1111</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIII-04906</x:t>
   </x:si>
   <x:si>
     <x:t>61-1-2026-1020-914</x:t>
+  </x:si>
+  <x:si>
+    <x:t>125646</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIII-04692</x:t>
@@ -147,7 +159,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -216,13 +228,6 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
@@ -474,7 +479,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="28">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -515,50 +520,41 @@
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -606,6 +602,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -617,71 +617,55 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1062,7 +1046,7 @@
       <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s"/>
+      <x:c r="D8" s="15" t="s"/>
       <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1072,23 +1056,23 @@
       <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46035.1020949074</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>46035.1021180556</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1231234312123</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="H8" s="16">
+        <x:v>46035.1021040857</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>46035.102121169</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46035.1127430556</x:v>
+      <x:c r="L8" s="18">
+        <x:v>46035.1127504861</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -1096,203 +1080,203 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s"/>
+      <x:c r="E9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46035.3508730903</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>46035.3508911111</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L9" s="18">
+        <x:v>46035.3565969097</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46035.3508680556</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>46035.3508796296</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>5555</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46035.3565856482</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C10" s="17" t="s">
+      <x:c r="B10" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D10" s="18" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E10" s="17" t="s">
+      <x:c r="D10" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
-        <x:v>46040.9500115741</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>46040.9500462963</x:v>
-      </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1111</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="F10" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46040.9500125116</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>46040.9500471991</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>46040.9546990741</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="L10" s="18">
+        <x:v>46040.9547064005</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
+      <x:c r="B11" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D11" s="18" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E11" s="17" t="s">
+      <x:c r="D11" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H11" s="19">
-        <x:v>46036.033587963</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>46036.0336226852</x:v>
-      </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>125646</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="F11" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46036.033594456</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46036.0336262963</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L11" s="21">
-        <x:v>46036.037337963</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="L11" s="18">
+        <x:v>46036.0373402083</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="s">
+      <x:c r="B12" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D12" s="18" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E12" s="17" t="s">
+      <x:c r="D12" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H12" s="19">
-        <x:v>46030.3123263889</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
-        <x:v>46030.3123611111</x:v>
-      </x:c>
-      <x:c r="J12" s="18" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
+      <x:c r="F12" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46030.3123357639</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>46030.3123672106</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L12" s="21">
-        <x:v>46030.5666550926</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="L12" s="18">
+        <x:v>46030.5666564468</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="22" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="24" t="s"/>
+      <x:c r="B15" s="19" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C15" s="20" t="s"/>
+      <x:c r="D15" s="20" t="s"/>
+      <x:c r="E15" s="21" t="s"/>
+      <x:c r="F15" s="21" t="s"/>
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="s">
-        <x:v>36</x:v>
+      <x:c r="B16" s="22" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C16" s="23" t="s"/>
+      <x:c r="D16" s="23" t="s"/>
+      <x:c r="E16" s="23" t="s"/>
+      <x:c r="F16" s="24" t="s">
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="28" t="s">
+      <x:c r="B17" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C17" s="29" t="s"/>
-      <x:c r="D17" s="29" t="s"/>
-      <x:c r="E17" s="29" t="s"/>
-      <x:c r="F17" s="30" t="n">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="28" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C18" s="29" t="s"/>
-      <x:c r="D18" s="29" t="s"/>
-      <x:c r="E18" s="29" t="s"/>
-      <x:c r="F18" s="30" t="n">
+      <x:c r="B18" s="25" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="31" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C19" s="32" t="s"/>
-      <x:c r="D19" s="32" t="s"/>
-      <x:c r="E19" s="32" t="s"/>
-      <x:c r="F19" s="33" t="n">
+      <x:c r="B19" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C19" s="29" t="s"/>
+      <x:c r="D19" s="29" t="s"/>
+      <x:c r="E19" s="29" t="s"/>
+      <x:c r="F19" s="30" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
@@ -998,7 +998,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1038,7 +1038,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -1075,7 +1075,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -1111,7 +1111,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
@@ -1149,7 +1149,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
@@ -1187,7 +1187,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>27</x:v>
       </x:c>

--- a/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <x:si>
-    <x:t>EVALUATOR SUMMARY</x:t>
+    <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
   <x:si>
     <x:t>EDWARD THEEVALUATOR</x:t>

--- a/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
@@ -22,15 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
   <x:si>
     <x:t>EDWARD THEEVALUATOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XIII | January 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -479,7 +476,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -496,6 +493,9 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -554,7 +554,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -590,6 +590,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -964,20 +968,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1000,283 +1004,283 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="D8" s="16" t="s"/>
+      <x:c r="E8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="H8" s="17">
+        <x:v>46035.1021040857</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>46035.102121169</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46035.1021040857</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>46035.102121169</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="K8" s="18" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>46035.1127504861</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>46035.1127504861</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="B9" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s"/>
+      <x:c r="E9" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="F9" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="G9" s="15" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="H9" s="17">
+        <x:v>46035.3508730903</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46035.3508911111</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46035.3508730903</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>46035.3508911111</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="K9" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L9" s="18">
+      <x:c r="L9" s="19">
         <x:v>46035.3565969097</x:v>
       </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="M9" s="15" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
+      <x:c r="B10" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="E10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="H10" s="17">
+        <x:v>46040.9500125116</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>46040.9500471991</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46040.9500125116</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46040.9500471991</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L10" s="18">
+      <x:c r="L10" s="19">
         <x:v>46040.9547064005</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="M10" s="15" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
+      <x:c r="B11" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C11" s="14" t="s">
+      <x:c r="E11" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
+      <x:c r="F11" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G11" s="14" t="s">
+      <x:c r="H11" s="17">
+        <x:v>46036.033594456</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>46036.0336262963</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46036.033594456</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46036.0336262963</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L11" s="18">
+      <x:c r="L11" s="19">
         <x:v>46036.0373402083</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="M11" s="15" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="14" t="s">
+      <x:c r="B12" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C12" s="14" t="s">
+      <x:c r="E12" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
+      <x:c r="F12" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="G12" s="14" t="s">
+      <x:c r="H12" s="17">
+        <x:v>46030.3123357639</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>46030.3123672106</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46030.3123357639</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46030.3123672106</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
+      <x:c r="K12" s="18" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L12" s="18">
+      <x:c r="L12" s="19">
         <x:v>46030.5666564468</x:v>
       </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="M12" s="15" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="19" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C15" s="20" t="s"/>
-      <x:c r="D15" s="20" t="s"/>
-      <x:c r="E15" s="21" t="s"/>
-      <x:c r="F15" s="21" t="s"/>
+      <x:c r="B15" s="20" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C15" s="21" t="s"/>
+      <x:c r="D15" s="21" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="22" t="s"/>
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="22" t="s">
+      <x:c r="B16" s="23" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C16" s="24" t="s"/>
+      <x:c r="D16" s="24" t="s"/>
+      <x:c r="E16" s="24" t="s"/>
+      <x:c r="F16" s="25" t="s">
         <x:v>39</x:v>
-      </x:c>
-      <x:c r="C16" s="23" t="s"/>
-      <x:c r="D16" s="23" t="s"/>
-      <x:c r="E16" s="23" t="s"/>
-      <x:c r="F16" s="24" t="s">
-        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="n">
+      <x:c r="B17" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="25" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C18" s="26" t="s"/>
-      <x:c r="D18" s="26" t="s"/>
-      <x:c r="E18" s="26" t="s"/>
-      <x:c r="F18" s="27" t="n">
+      <x:c r="B18" s="26" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="28" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C19" s="29" t="s"/>
-      <x:c r="D19" s="29" t="s"/>
-      <x:c r="E19" s="29" t="s"/>
-      <x:c r="F19" s="30" t="n">
+      <x:c r="B19" s="29" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C19" s="30" t="s"/>
+      <x:c r="D19" s="30" t="s"/>
+      <x:c r="E19" s="30" t="s"/>
+      <x:c r="F19" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-EDWARD-THEEVALUATOR-evaluator-cache-serviceTracking-EDWARD-THEEVALUATOR-XIII-202501-202612.xlsx
@@ -156,7 +156,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -196,14 +196,6 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -476,7 +468,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -487,16 +479,13 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -508,53 +497,53 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -589,87 +578,83 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -971,17 +956,17 @@
       <x:c r="B5" s="12">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1004,283 +989,283 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s"/>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="D8" s="15" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46035.1021040857</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>46035.102121169</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46035.1127504861</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s"/>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="D9" s="15" t="s"/>
+      <x:c r="E9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46035.3508730903</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46035.3508911111</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46035.3565969097</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>46040.9500125116</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>46040.9500471991</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>46040.9547064005</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>46036.033594456</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>46036.0336262963</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>46036.0373402083</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>46030.3123357639</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>46030.3123672106</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>46030.5666564468</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="20" t="s">
+      <x:c r="B15" s="19" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C15" s="21" t="s"/>
-      <x:c r="D15" s="21" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="22" t="s"/>
+      <x:c r="C15" s="20" t="s"/>
+      <x:c r="D15" s="20" t="s"/>
+      <x:c r="E15" s="21" t="s"/>
+      <x:c r="F15" s="21" t="s"/>
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="23" t="s">
+      <x:c r="B16" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C16" s="24" t="s"/>
-      <x:c r="D16" s="24" t="s"/>
-      <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="25" t="s">
+      <x:c r="C16" s="23" t="s"/>
+      <x:c r="D16" s="23" t="s"/>
+      <x:c r="E16" s="23" t="s"/>
+      <x:c r="F16" s="24" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
+      <x:c r="B17" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
+      <x:c r="B18" s="25" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="29" t="s">
+      <x:c r="B19" s="28" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C19" s="30" t="s"/>
-      <x:c r="D19" s="30" t="s"/>
-      <x:c r="E19" s="30" t="s"/>
-      <x:c r="F19" s="31" t="n">
+      <x:c r="C19" s="29" t="s"/>
+      <x:c r="D19" s="29" t="s"/>
+      <x:c r="E19" s="29" t="s"/>
+      <x:c r="F19" s="30" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
